--- a/supplementary-materials/shooting_game.xlsx
+++ b/supplementary-materials/shooting_game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ict15\Desktop\プログラム学習\0805\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ict15\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A515AB24-0853-4C89-86AA-06337FF0B8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A90C23A-31C4-4466-822C-9EE353011A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{A367ECF4-BD78-4C98-AC70-016D98DE0B9E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{A367ECF4-BD78-4C98-AC70-016D98DE0B9E}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="16" r:id="rId1"/>
@@ -496,10 +496,6 @@
   </si>
   <si>
     <t>タイトル</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ケームオーバー</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1677,6 +1673,10 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ゲームオーバー</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -9928,7 +9928,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7324725" y="238125"/>
+          <a:off x="7400925" y="476250"/>
           <a:ext cx="5190476" cy="4942857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10273,7 +10273,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>= gamePver </a:t>
+            <a:t>= gameOver </a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
@@ -30993,122 +30993,122 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
         <v>83</v>
       </c>
-      <c r="E7" t="s">
-        <v>84</v>
-      </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -31223,57 +31223,57 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="L10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
@@ -31281,31 +31281,31 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" t="s">
         <v>64</v>
       </c>
-      <c r="K17" t="s">
-        <v>65</v>
-      </c>
       <c r="R17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="R32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="18:18" x14ac:dyDescent="0.4">
       <c r="R33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -31322,25 +31322,25 @@
   <sheetData>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -31361,10 +31361,10 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
@@ -31381,7 +31381,7 @@
         <v>39</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
@@ -31398,7 +31398,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
@@ -31415,7 +31415,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
@@ -31432,7 +31432,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
@@ -31466,10 +31466,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
@@ -31486,10 +31486,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
@@ -31506,10 +31506,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
@@ -31526,7 +31526,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
@@ -31534,29 +31534,29 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -31573,12 +31573,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -31602,263 +31602,263 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>121</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>131</v>
-      </c>
       <c r="D4" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>133</v>
-      </c>
       <c r="E10" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -31879,7 +31879,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="6:6" x14ac:dyDescent="0.4">
@@ -31901,7 +31901,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -31918,7 +31918,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -31935,7 +31935,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
